--- a/testdata/pim_data.xlsx
+++ b/testdata/pim_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srout\Desktop\SONALI\Personal\SelfLearning\PythonWithSeleniumTraining\udemy\ZSeleniumFramework\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C52F56A-18C4-488D-9ECD-020862AC74DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D2793E5-2CE8-41C7-AA4A-F528F1DC5195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,13 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
-  <si>
-    <t>expected</t>
-  </si>
-  <si>
-    <t>Admin</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
   <si>
     <t>emp_id</t>
   </si>
@@ -365,35 +359,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3">
-        <v>11111</v>
-      </c>
-      <c r="B3" t="b">
-        <v>0</v>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" s="2">
+        <v>777</v>
       </c>
     </row>
   </sheetData>
